--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.44190760276759</v>
+        <v>2.996809985449733</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6031057235556</v>
+        <v>2.860504680077785</v>
       </c>
       <c r="E2" t="n">
-        <v>1.988092940128645</v>
+        <v>0.3230651027709048</v>
       </c>
       <c r="F2" t="n">
-        <v>1.402795111485823</v>
+        <v>0.2279542056164463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.4657217225103</v>
+        <v>2.350679779907923</v>
       </c>
       <c r="D3" t="n">
-        <v>14.79751550058395</v>
+        <v>2.404596268844893</v>
       </c>
       <c r="E3" t="n">
-        <v>1.988092940128645</v>
+        <v>0.3230651027709048</v>
       </c>
       <c r="F3" t="n">
-        <v>1.402795111485823</v>
+        <v>0.2279542056164463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
